--- a/`12611227.xlsx
+++ b/`12611227.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saurabh kumar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saurabh kumar\Desktop\Daily Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t xml:space="preserve">feeling not so good and also feel tied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling good after the class is over </t>
   </si>
 </sst>
 </file>
@@ -1575,27 +1578,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B18" s="14">
+        <v>320</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>40</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>40</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>

--- a/`12611227.xlsx
+++ b/`12611227.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1624,27 +1624,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>42</v>
+      </c>
+      <c r="D19" s="14">
+        <v>123</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>

--- a/`12611227.xlsx
+++ b/`12611227.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t xml:space="preserve">feeling good after the class is over </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fell good after class over.today is full of working day</t>
   </si>
 </sst>
 </file>
@@ -1670,27 +1673,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>45</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>40</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
